--- a/examples/jpetstore-6/.understand-anything/doc-output/si-프로그램목록.xlsx
+++ b/examples/jpetstore-6/.understand-anything/doc-output/si-프로그램목록.xlsx
@@ -2,8 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="프로그램 목록" sheetId="1" r:id="rId1"/>
-    <sheet name="규모산정(FP) 기초" sheetId="2" r:id="rId2"/>
+    <sheet name="문서정보" sheetId="1" r:id="rId1"/>
+    <sheet name="프로그램 목록" sheetId="2" r:id="rId2"/>
+    <sheet name="규모산정(FP) 기초" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -58,6 +59,102 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>내용</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>문서명</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SI 프로그램목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>방법론</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>si-standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>소스 커밋</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>[미확인]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>작성자 / 버전 / 작성일</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>[미확인] — 제출 전 사람이 채움</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>본 파일의 지위</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>정적 스캔 스냅샷(원천 데이터) — 대시보드에서의 확정 편집은 반영되지 않음. 최신화는 /understand-docs 재실행.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>신뢰도 표기</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>[확정]=정적 분석 근거(file:line) 보유, [추정]=추론, [미확인]=사람 채움 대상 — 사람 검수/사인오프 여부와 무관.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B7"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="23" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
@@ -3447,10 +3544,11 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:I75"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -4456,5 +4554,6 @@
       <c r="E37" s="2"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E37"/>
 </worksheet>
 </file>
--- a/examples/jpetstore-6/.understand-anything/doc-output/si-프로그램목록.xlsx
+++ b/examples/jpetstore-6/.understand-anything/doc-output/si-프로그램목록.xlsx
@@ -1296,12 +1296,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PGM-MAP-b9fcb7db</t>
+          <t>PGM-SCR-03dd742b</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>index</t>
+          <t>AccountActionBean</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1311,21 +1311,21 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>[미확인]</t>
+          <t>account</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>SQL매퍼</t>
+          <t>화면</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>api</t>
         </is>
       </c>
       <c r="G26">
-        <v>448</v>
+        <v>208</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1334,19 +1334,19 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>src/site/es/xdoc/index.xml:1</t>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/AccountActionBean.java:1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PGM-MAP-522f2153</t>
+          <t>PGM-SCR-6c5edc23</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>index</t>
+          <t>CartActionBean</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1356,21 +1356,21 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>[미확인]</t>
+          <t>cart</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SQL매퍼</t>
+          <t>화면</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>api</t>
         </is>
       </c>
       <c r="G27">
-        <v>406</v>
+        <v>150</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1379,19 +1379,19 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>src/site/ja/xdoc/index.xml:1</t>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/CartActionBean.java:1</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PGM-MAP-04dfefa3</t>
+          <t>PGM-SCR-1de6f314</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>index</t>
+          <t>CatalogActionBean</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1401,21 +1401,21 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>[미확인]</t>
+          <t>catalog</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>SQL매퍼</t>
+          <t>화면</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>api</t>
         </is>
       </c>
       <c r="G28">
-        <v>408</v>
+        <v>219</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1424,19 +1424,19 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>src/site/ko/xdoc/index.xml:1</t>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/CatalogActionBean.java:1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PGM-MAP-40db7297</t>
+          <t>PGM-SCR-fc9c602d</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>index</t>
+          <t>OrderActionBean</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1446,21 +1446,21 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>[미확인]</t>
+          <t>order</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SQL매퍼</t>
+          <t>화면</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>api</t>
         </is>
       </c>
       <c r="G29">
-        <v>448</v>
+        <v>197</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1469,19 +1469,19 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>src/site/xdoc/index.xml:1</t>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/OrderActionBean.java:1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PGM-SCR-03dd742b</t>
+          <t>PGM-SCR-3b60f781</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>AccountActionBean</t>
+          <t>EditAccountForm</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>account</t>
+          <t>web-inf [추정]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1501,11 +1501,11 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="G30">
-        <v>208</v>
+        <v>48</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1514,19 +1514,19 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>src/main/java/org/mybatis/jpetstore/web/actions/AccountActionBean.java:1</t>
+          <t>src/main/webapp/WEB-INF/jsp/account/EditAccountForm.jsp:1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PGM-SCR-6c5edc23</t>
+          <t>PGM-SCR-17377901</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CartActionBean</t>
+          <t>IncludeAccountFields</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>cart</t>
+          <t>web-inf [추정]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1546,11 +1546,11 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="G31">
-        <v>150</v>
+        <v>87</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -1559,19 +1559,19 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>src/main/java/org/mybatis/jpetstore/web/actions/CartActionBean.java:1</t>
+          <t>src/main/webapp/WEB-INF/jsp/account/IncludeAccountFields.jsp:1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PGM-SCR-1de6f314</t>
+          <t>PGM-SCR-4e391b64</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CatalogActionBean</t>
+          <t>NewAccountForm</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>catalog</t>
+          <t>web-inf [추정]</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1591,11 +1591,11 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="G32">
-        <v>219</v>
+        <v>47</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -1604,19 +1604,19 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>src/main/java/org/mybatis/jpetstore/web/actions/CatalogActionBean.java:1</t>
+          <t>src/main/webapp/WEB-INF/jsp/account/NewAccountForm.jsp:1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PGM-SCR-fc9c602d</t>
+          <t>PGM-SCR-42f29104</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>OrderActionBean</t>
+          <t>SignonForm</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>order</t>
+          <t>web-inf [추정]</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1636,11 +1636,11 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="G33">
-        <v>197</v>
+        <v>34</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -1649,19 +1649,19 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>src/main/java/org/mybatis/jpetstore/web/actions/OrderActionBean.java:1</t>
+          <t>src/main/webapp/WEB-INF/jsp/account/SignonForm.jsp:1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PGM-SCR-3b60f781</t>
+          <t>PGM-SCR-3c93f7f6</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>EditAccountForm</t>
+          <t>Cart</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="G34">
-        <v>48</v>
+        <v>105</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -1694,19 +1694,19 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>src/main/webapp/WEB-INF/jsp/account/EditAccountForm.jsp:1</t>
+          <t>src/main/webapp/WEB-INF/jsp/cart/Cart.jsp:1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PGM-SCR-17377901</t>
+          <t>PGM-SCR-54cf59fc</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>IncludeAccountFields</t>
+          <t>Checkout</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="G35">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -1739,19 +1739,19 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>src/main/webapp/WEB-INF/jsp/account/IncludeAccountFields.jsp:1</t>
+          <t>src/main/webapp/WEB-INF/jsp/cart/Checkout.jsp:1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>PGM-SCR-4e391b64</t>
+          <t>PGM-SCR-f9a81dbb</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>NewAccountForm</t>
+          <t>IncludeMyList</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="G36">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -1784,19 +1784,19 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>src/main/webapp/WEB-INF/jsp/account/NewAccountForm.jsp:1</t>
+          <t>src/main/webapp/WEB-INF/jsp/cart/IncludeMyList.jsp:1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>PGM-SCR-42f29104</t>
+          <t>PGM-SCR-a2276880</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SignonForm</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="G37">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -1829,19 +1829,19 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>src/main/webapp/WEB-INF/jsp/account/SignonForm.jsp:1</t>
+          <t>src/main/webapp/WEB-INF/jsp/catalog/Category.jsp:1</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PGM-SCR-3c93f7f6</t>
+          <t>PGM-SCR-340aa6e6</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Cart</t>
+          <t>Item</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1865,7 +1865,7 @@
         </is>
       </c>
       <c r="G38">
-        <v>105</v>
+        <v>72</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -1874,19 +1874,19 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>src/main/webapp/WEB-INF/jsp/cart/Cart.jsp:1</t>
+          <t>src/main/webapp/WEB-INF/jsp/catalog/Item.jsp:1</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PGM-SCR-54cf59fc</t>
+          <t>PGM-SCR-b1ada8ee</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Checkout</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1910,7 +1910,7 @@
         </is>
       </c>
       <c r="G39">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -1919,19 +1919,19 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>src/main/webapp/WEB-INF/jsp/cart/Checkout.jsp:1</t>
+          <t>src/main/webapp/WEB-INF/jsp/catalog/Main.jsp:1</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PGM-SCR-f9a81dbb</t>
+          <t>PGM-SCR-807f6244</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>IncludeMyList</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="G40">
-        <v>32</v>
+        <v>77</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -1964,19 +1964,19 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>src/main/webapp/WEB-INF/jsp/cart/IncludeMyList.jsp:1</t>
+          <t>src/main/webapp/WEB-INF/jsp/catalog/Product.jsp:1</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>PGM-SCR-a2276880</t>
+          <t>PGM-SCR-2fc8e576</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>SearchProducts</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2000,7 +2000,7 @@
         </is>
       </c>
       <c r="G41">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -2009,19 +2009,19 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>src/main/webapp/WEB-INF/jsp/catalog/Category.jsp:1</t>
+          <t>src/main/webapp/WEB-INF/jsp/catalog/SearchProducts.jsp:1</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PGM-SCR-340aa6e6</t>
+          <t>PGM-SCR-9d95f4c3</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>Error</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="G42">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -2054,19 +2054,19 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>src/main/webapp/WEB-INF/jsp/catalog/Item.jsp:1</t>
+          <t>src/main/webapp/WEB-INF/jsp/common/Error.jsp:1</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PGM-SCR-b1ada8ee</t>
+          <t>PGM-SCR-699ba88b</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>IncludeBottom</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="G43">
-        <v>92</v>
+        <v>36</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -2099,19 +2099,19 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>src/main/webapp/WEB-INF/jsp/catalog/Main.jsp:1</t>
+          <t>src/main/webapp/WEB-INF/jsp/common/IncludeBottom.jsp:1</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PGM-SCR-807f6244</t>
+          <t>PGM-SCR-9a011004</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>IncludeTop</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="G44">
-        <v>77</v>
+        <v>131</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -2144,19 +2144,19 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>src/main/webapp/WEB-INF/jsp/catalog/Product.jsp:1</t>
+          <t>src/main/webapp/WEB-INF/jsp/common/IncludeTop.jsp:1</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PGM-SCR-2fc8e576</t>
+          <t>PGM-SCR-ed0c6c14</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SearchProducts</t>
+          <t>ConfirmOrder</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2180,7 +2180,7 @@
         </is>
       </c>
       <c r="G45">
-        <v>62</v>
+        <v>122</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -2189,19 +2189,19 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>src/main/webapp/WEB-INF/jsp/catalog/SearchProducts.jsp:1</t>
+          <t>src/main/webapp/WEB-INF/jsp/order/ConfirmOrder.jsp:1</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>PGM-SCR-9d95f4c3</t>
+          <t>PGM-SCR-d0ad3de3</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>ListOrders</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="G46">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -2234,19 +2234,19 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>src/main/webapp/WEB-INF/jsp/common/Error.jsp:1</t>
+          <t>src/main/webapp/WEB-INF/jsp/order/ListOrders.jsp:1</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>PGM-SCR-699ba88b</t>
+          <t>PGM-SCR-26b9e12b</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>IncludeBottom</t>
+          <t>NewOrderForm</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2270,7 +2270,7 @@
         </is>
       </c>
       <c r="G47">
-        <v>36</v>
+        <v>91</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -2279,19 +2279,19 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>src/main/webapp/WEB-INF/jsp/common/IncludeBottom.jsp:1</t>
+          <t>src/main/webapp/WEB-INF/jsp/order/NewOrderForm.jsp:1</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>PGM-SCR-9a011004</t>
+          <t>PGM-SCR-e3e1963d</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>IncludeTop</t>
+          <t>ShippingForm</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="G48">
-        <v>131</v>
+        <v>68</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -2324,19 +2324,19 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>src/main/webapp/WEB-INF/jsp/common/IncludeTop.jsp:1</t>
+          <t>src/main/webapp/WEB-INF/jsp/order/ShippingForm.jsp:1</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PGM-SCR-ed0c6c14</t>
+          <t>PGM-SCR-dbbf9812</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ConfirmOrder</t>
+          <t>ViewOrder</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="G49">
-        <v>122</v>
+        <v>173</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -2369,19 +2369,19 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>src/main/webapp/WEB-INF/jsp/order/ConfirmOrder.jsp:1</t>
+          <t>src/main/webapp/WEB-INF/jsp/order/ViewOrder.jsp:1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PGM-SCR-d0ad3de3</t>
+          <t>PGM-SCR-f1c1b2e3</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ListOrders</t>
+          <t>web</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>web-inf [추정]</t>
+          <t>web-inf</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2401,11 +2401,11 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>api</t>
         </is>
       </c>
       <c r="G50">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -2414,19 +2414,19 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>src/main/webapp/WEB-INF/jsp/order/ListOrders.jsp:1</t>
+          <t>src/main/webapp/WEB-INF/web.xml:1</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PGM-SCR-26b9e12b</t>
+          <t>PGM-SVC-5f5bf3cb</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NewOrderForm</t>
+          <t>AccountService</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2436,21 +2436,21 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>web-inf [추정]</t>
+          <t>account</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>화면</t>
+          <t>서비스</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>service</t>
         </is>
       </c>
       <c r="G51">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -2459,19 +2459,19 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>src/main/webapp/WEB-INF/jsp/order/NewOrderForm.jsp:1</t>
+          <t>src/main/java/org/mybatis/jpetstore/service/AccountService.java:1</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>PGM-SCR-e3e1963d</t>
+          <t>PGM-SVC-2d117c4e</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ShippingForm</t>
+          <t>CatalogService</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2481,21 +2481,21 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>web-inf [추정]</t>
+          <t>공용(account+cart+catalog)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>화면</t>
+          <t>서비스</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>service</t>
         </is>
       </c>
       <c r="G52">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -2504,19 +2504,19 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>src/main/webapp/WEB-INF/jsp/order/ShippingForm.jsp:1</t>
+          <t>src/main/java/org/mybatis/jpetstore/service/CatalogService.java:1</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>PGM-SCR-dbbf9812</t>
+          <t>PGM-SVC-d564b236</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ViewOrder</t>
+          <t>OrderService</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2526,21 +2526,21 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>web-inf [추정]</t>
+          <t>order</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>화면</t>
+          <t>서비스</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>service</t>
         </is>
       </c>
       <c r="G53">
-        <v>173</v>
+        <v>132</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -2549,19 +2549,19 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>src/main/webapp/WEB-INF/jsp/order/ViewOrder.jsp:1</t>
+          <t>src/main/java/org/mybatis/jpetstore/service/OrderService.java:1</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>PGM-SCR-f1c1b2e3</t>
+          <t>PGM-TST-cbd3b9bd</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>ScreenTransitionIT</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2571,21 +2571,21 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>web-inf</t>
+          <t>[미확인]</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>화면</t>
+          <t>테스트</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="G54">
-        <v>64</v>
+        <v>444</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -2594,19 +2594,19 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>src/main/webapp/WEB-INF/web.xml:1</t>
+          <t>src/test/java/org/mybatis/jpetstore/ScreenTransitionIT.java:1</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>PGM-SVC-5f5bf3cb</t>
+          <t>PGM-TST-a07ed547</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>AccountService</t>
+          <t>CartTest</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2616,21 +2616,21 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>account</t>
+          <t>cart [추정]</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>서비스</t>
+          <t>테스트</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="G55">
-        <v>75</v>
+        <v>187</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -2639,19 +2639,19 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>src/main/java/org/mybatis/jpetstore/service/AccountService.java:1</t>
+          <t>src/test/java/org/mybatis/jpetstore/domain/CartTest.java:1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>PGM-SVC-2d117c4e</t>
+          <t>PGM-TST-43e068a3</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CatalogService</t>
+          <t>OrderTest</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2661,21 +2661,21 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>공용(account+cart+catalog)</t>
+          <t>order [추정]</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>서비스</t>
+          <t>테스트</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="G56">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -2684,19 +2684,19 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>src/main/java/org/mybatis/jpetstore/service/CatalogService.java:1</t>
+          <t>src/test/java/org/mybatis/jpetstore/domain/OrderTest.java:1</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>PGM-SVC-d564b236</t>
+          <t>PGM-TST-51d18a8f</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>OrderService</t>
+          <t>AccountMapperTest</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2706,21 +2706,21 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>order</t>
+          <t>account [추정]</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>서비스</t>
+          <t>테스트</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="G57">
-        <v>132</v>
+        <v>248</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -2729,19 +2729,19 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>src/main/java/org/mybatis/jpetstore/service/OrderService.java:1</t>
+          <t>src/test/java/org/mybatis/jpetstore/mapper/AccountMapperTest.java:1</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PGM-TST-cbd3b9bd</t>
+          <t>PGM-TST-51e4435e</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ScreenTransitionIT</t>
+          <t>CategoryMapperTest</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="G58">
-        <v>444</v>
+        <v>86</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -2774,19 +2774,19 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>src/test/java/org/mybatis/jpetstore/ScreenTransitionIT.java:1</t>
+          <t>src/test/java/org/mybatis/jpetstore/mapper/CategoryMapperTest.java:1</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PGM-TST-a07ed547</t>
+          <t>PGM-TST-b62ae196</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CartTest</t>
+          <t>ItemMapperTest</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>cart [추정]</t>
+          <t>[미확인]</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2810,7 +2810,7 @@
         </is>
       </c>
       <c r="G59">
-        <v>187</v>
+        <v>145</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -2819,19 +2819,19 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>src/test/java/org/mybatis/jpetstore/domain/CartTest.java:1</t>
+          <t>src/test/java/org/mybatis/jpetstore/mapper/ItemMapperTest.java:1</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PGM-TST-43e068a3</t>
+          <t>PGM-TST-e6e6d949</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>OrderTest</t>
+          <t>LineItemMapperTest</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>order [추정]</t>
+          <t>[미확인]</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="G60">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -2864,19 +2864,19 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>src/test/java/org/mybatis/jpetstore/domain/OrderTest.java:1</t>
+          <t>src/test/java/org/mybatis/jpetstore/mapper/LineItemMapperTest.java:1</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>PGM-TST-51d18a8f</t>
+          <t>PGM-TST-08126415</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>AccountMapperTest</t>
+          <t>MapperTestContext</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>account [추정]</t>
+          <t>[미확인]</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="G61">
-        <v>248</v>
+        <v>59</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -2909,19 +2909,19 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>src/test/java/org/mybatis/jpetstore/mapper/AccountMapperTest.java:1</t>
+          <t>src/test/java/org/mybatis/jpetstore/mapper/MapperTestContext.java:1</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>PGM-TST-51e4435e</t>
+          <t>PGM-TST-35bb0746</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CategoryMapperTest</t>
+          <t>OrderMapperTest</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>[미확인]</t>
+          <t>order [추정]</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2945,7 +2945,7 @@
         </is>
       </c>
       <c r="G62">
-        <v>86</v>
+        <v>247</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -2954,19 +2954,19 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>src/test/java/org/mybatis/jpetstore/mapper/CategoryMapperTest.java:1</t>
+          <t>src/test/java/org/mybatis/jpetstore/mapper/OrderMapperTest.java:1</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>PGM-TST-b62ae196</t>
+          <t>PGM-TST-4bc9630d</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ItemMapperTest</t>
+          <t>ProductMapperTest</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2990,7 +2990,7 @@
         </is>
       </c>
       <c r="G63">
-        <v>145</v>
+        <v>113</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -2999,19 +2999,19 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>src/test/java/org/mybatis/jpetstore/mapper/ItemMapperTest.java:1</t>
+          <t>src/test/java/org/mybatis/jpetstore/mapper/ProductMapperTest.java:1</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>PGM-TST-e6e6d949</t>
+          <t>PGM-TST-2b457cae</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>LineItemMapperTest</t>
+          <t>SequenceMapperTest</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="G64">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -3044,19 +3044,19 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>src/test/java/org/mybatis/jpetstore/mapper/LineItemMapperTest.java:1</t>
+          <t>src/test/java/org/mybatis/jpetstore/mapper/SequenceMapperTest.java:1</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>PGM-TST-08126415</t>
+          <t>PGM-TST-ee985e74</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MapperTestContext</t>
+          <t>AccountServiceTest</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>[미확인]</t>
+          <t>account [추정]</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3080,7 +3080,7 @@
         </is>
       </c>
       <c r="G65">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -3089,19 +3089,19 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>src/test/java/org/mybatis/jpetstore/mapper/MapperTestContext.java:1</t>
+          <t>src/test/java/org/mybatis/jpetstore/service/AccountServiceTest.java:1</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>PGM-TST-35bb0746</t>
+          <t>PGM-TST-9b9b47d6</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>OrderMapperTest</t>
+          <t>CatalogServiceTest</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>order [추정]</t>
+          <t>catalog [추정]</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3125,7 +3125,7 @@
         </is>
       </c>
       <c r="G66">
-        <v>247</v>
+        <v>193</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -3134,19 +3134,19 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>src/test/java/org/mybatis/jpetstore/mapper/OrderMapperTest.java:1</t>
+          <t>src/test/java/org/mybatis/jpetstore/service/CatalogServiceTest.java:1</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>PGM-TST-4bc9630d</t>
+          <t>PGM-TST-f771cf2d</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ProductMapperTest</t>
+          <t>OrderServiceTest</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>[미확인]</t>
+          <t>order [추정]</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="G67">
-        <v>113</v>
+        <v>181</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -3179,19 +3179,19 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>src/test/java/org/mybatis/jpetstore/mapper/ProductMapperTest.java:1</t>
+          <t>src/test/java/org/mybatis/jpetstore/service/OrderServiceTest.java:1</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>PGM-TST-2b457cae</t>
+          <t>PGM-TST-8d655dc7</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SequenceMapperTest</t>
+          <t>AccountActionBeanTest</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>[미확인]</t>
+          <t>account [추정]</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="G68">
-        <v>65</v>
+        <v>116</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -3224,19 +3224,19 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>src/test/java/org/mybatis/jpetstore/mapper/SequenceMapperTest.java:1</t>
+          <t>src/test/java/org/mybatis/jpetstore/web/actions/AccountActionBeanTest.java:1</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>PGM-TST-ee985e74</t>
+          <t>PGM-TST-8016b806</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>AccountServiceTest</t>
+          <t>CartActionBeanTest</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>account [추정]</t>
+          <t>cart [추정]</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3260,7 +3260,7 @@
         </is>
       </c>
       <c r="G69">
-        <v>101</v>
+        <v>143</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -3269,19 +3269,19 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>src/test/java/org/mybatis/jpetstore/service/AccountServiceTest.java:1</t>
+          <t>src/test/java/org/mybatis/jpetstore/web/actions/CartActionBeanTest.java:1</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>PGM-TST-9b9b47d6</t>
+          <t>PGM-TST-bd08f434</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CatalogServiceTest</t>
+          <t>CatalogActionBeanTest</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="G70">
-        <v>193</v>
+        <v>155</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -3314,19 +3314,19 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>src/test/java/org/mybatis/jpetstore/service/CatalogServiceTest.java:1</t>
+          <t>src/test/java/org/mybatis/jpetstore/web/actions/CatalogActionBeanTest.java:1</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>PGM-TST-f771cf2d</t>
+          <t>PGM-TST-39fc6042</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>OrderServiceTest</t>
+          <t>OrderActionBeanTest</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3350,7 +3350,7 @@
         </is>
       </c>
       <c r="G71">
-        <v>181</v>
+        <v>72</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -3359,192 +3359,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>src/test/java/org/mybatis/jpetstore/service/OrderServiceTest.java:1</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>PGM-TST-8d655dc7</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>AccountActionBeanTest</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>[미확인]</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>account [추정]</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>테스트</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="G72">
-        <v>116</v>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>[확정]</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>src/test/java/org/mybatis/jpetstore/web/actions/AccountActionBeanTest.java:1</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>PGM-TST-8016b806</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>CartActionBeanTest</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>[미확인]</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>cart [추정]</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>테스트</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="G73">
-        <v>143</v>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>[확정]</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>src/test/java/org/mybatis/jpetstore/web/actions/CartActionBeanTest.java:1</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>PGM-TST-bd08f434</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>CatalogActionBeanTest</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>[미확인]</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>catalog [추정]</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>테스트</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="G74">
-        <v>155</v>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>[확정]</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>src/test/java/org/mybatis/jpetstore/web/actions/CatalogActionBeanTest.java:1</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>PGM-TST-39fc6042</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>OrderActionBeanTest</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>[미확인]</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>order [추정]</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>테스트</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="G75">
-        <v>72</v>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>[확정]</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
           <t>src/test/java/org/mybatis/jpetstore/web/actions/OrderActionBeanTest.java:1</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I75"/>
+  <autoFilter ref="A1:I71"/>
 </worksheet>
 </file>
 

--- a/examples/jpetstore-6/.understand-anything/doc-output/si-프로그램목록.xlsx
+++ b/examples/jpetstore-6/.understand-anything/doc-output/si-프로그램목록.xlsx
@@ -107,7 +107,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[미확인]</t>
+          <t>dfbb9822f7c17f41a39e96704f4ea4f455580278</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>web-inf [추정]</t>
+          <t>account [추정]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>web-inf [추정]</t>
+          <t>account [추정]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>web-inf [추정]</t>
+          <t>account [추정]</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>web-inf [추정]</t>
+          <t>account [추정]</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>web-inf [추정]</t>
+          <t>cart [추정]</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>web-inf [추정]</t>
+          <t>cart [추정]</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>web-inf [추정]</t>
+          <t>cart [추정]</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>web-inf [추정]</t>
+          <t>catalog [추정]</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>web-inf [추정]</t>
+          <t>catalog [추정]</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>web-inf [추정]</t>
+          <t>catalog [추정]</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>web-inf [추정]</t>
+          <t>catalog [추정]</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>web-inf [추정]</t>
+          <t>catalog [추정]</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>web-inf [추정]</t>
+          <t>[미확인]</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>web-inf [추정]</t>
+          <t>[미확인]</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>web-inf [추정]</t>
+          <t>[미확인]</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>web-inf [추정]</t>
+          <t>order [추정]</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>web-inf [추정]</t>
+          <t>order [추정]</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>web-inf [추정]</t>
+          <t>order [추정]</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>web-inf [추정]</t>
+          <t>order [추정]</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>web-inf [추정]</t>
+          <t>order [추정]</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>web-inf</t>
+          <t>web</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
